--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7937,0.0252,0.0979,0.0627</t>
-  </si>
-  <si>
-    <t>0.0354,0.0101,0.0039,0.9824</t>
-  </si>
-  <si>
-    <t>0.6738,0.0967,0.0286,0.2320</t>
-  </si>
-  <si>
-    <t>0.1011,0.0092,0.0036,0.9553</t>
-  </si>
-  <si>
-    <t>0.9925,0.0028,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9885,0.0133,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9799,0.0176,0.0019,0.0014</t>
-  </si>
-  <si>
-    <t>0.9938,0.0037,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9782,0.0177,0.0023,0.0026</t>
-  </si>
-  <si>
-    <t>0.9776,0.0219,0.0023,0.0015</t>
-  </si>
-  <si>
-    <t>0.9889,0.0044,0.0010,0.0023</t>
-  </si>
-  <si>
-    <t>0.9952,0.0026,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.7240,0.0953,0.1321,0.0252</t>
-  </si>
-  <si>
-    <t>0.4045,0.0593,0.6369,0.0065</t>
-  </si>
-  <si>
-    <t>0.2390,0.0356,0.8335,0.0020</t>
-  </si>
-  <si>
-    <t>0.3644,0.0405,0.6970,0.0076</t>
-  </si>
-  <si>
-    <t>0.6716,0.0626,0.3077,0.0146</t>
-  </si>
-  <si>
-    <t>0.0130,0.9805,0.0101,0.0003</t>
-  </si>
-  <si>
-    <t>0.0500,0.9422,0.0257,0.0007</t>
-  </si>
-  <si>
-    <t>0.1145,0.8749,0.0483,0.0033</t>
-  </si>
-  <si>
-    <t>0.0042,0.9879,0.0117,0.0006</t>
-  </si>
-  <si>
-    <t>0.0067,0.9867,0.0200,0.0001</t>
-  </si>
-  <si>
-    <t>0.3910,0.0141,0.7053,0.0102</t>
-  </si>
-  <si>
-    <t>0.4884,0.0099,0.7265,0.0017</t>
-  </si>
-  <si>
-    <t>0.0812,0.0062,0.9402,0.0032</t>
-  </si>
-  <si>
-    <t>0.3388,0.0189,0.7563,0.0054</t>
-  </si>
-  <si>
-    <t>0.0622,0.0028,0.9568,0.0033</t>
-  </si>
-  <si>
-    <t>0.0755,0.0081,0.9394,0.0051</t>
-  </si>
-  <si>
-    <t>0.0315,0.0012,0.9741,0.0041</t>
-  </si>
-  <si>
-    <t>0.5378,0.2753,0.1900,0.0068</t>
-  </si>
-  <si>
-    <t>0.2808,0.1933,0.6080,0.0035</t>
-  </si>
-  <si>
-    <t>0.0025,0.0074,0.9919,0.0060</t>
-  </si>
-  <si>
-    <t>0.0237,0.9048,0.1786,0.0006</t>
-  </si>
-  <si>
-    <t>0.8923,0.0680,0.0251,0.0109</t>
-  </si>
-  <si>
-    <t>0.3876,0.1962,0.4983,0.0133</t>
-  </si>
-  <si>
-    <t>0.3229,0.7161,0.0379,0.0029</t>
-  </si>
-  <si>
-    <t>0.0745,0.6874,0.5057,0.0059</t>
-  </si>
-  <si>
-    <t>0.0317,0.1727,0.8648,0.0211</t>
-  </si>
-  <si>
-    <t>0.0397,0.0049,0.9370,0.0164</t>
-  </si>
-  <si>
-    <t>0.1589,0.0532,0.8394,0.0014</t>
-  </si>
-  <si>
-    <t>0.3261,0.0186,0.7788,0.0034</t>
-  </si>
-  <si>
-    <t>0.1679,0.0449,0.8505,0.0026</t>
-  </si>
-  <si>
-    <t>0.1060,0.7473,0.2174,0.0077</t>
-  </si>
-  <si>
-    <t>0.0109,0.0029,0.9782,0.0083</t>
-  </si>
-  <si>
-    <t>0.0199,0.8980,0.0107,0.4140</t>
-  </si>
-  <si>
-    <t>0.0426,0.9333,0.0431,0.0017</t>
-  </si>
-  <si>
-    <t>0.0099,0.9541,0.1790,0.0009</t>
-  </si>
-  <si>
-    <t>0.0115,0.9523,0.2941,0.0012</t>
-  </si>
-  <si>
-    <t>0.0049,0.0388,0.9748,0.0147</t>
-  </si>
-  <si>
-    <t>0.0024,0.0252,0.9938,0.0007</t>
-  </si>
-  <si>
-    <t>0.0177,0.0107,0.9725,0.0050</t>
-  </si>
-  <si>
-    <t>0.0788,0.0059,0.9546,0.0015</t>
-  </si>
-  <si>
-    <t>0.0128,0.0114,0.9776,0.0045</t>
-  </si>
-  <si>
-    <t>0.0203,0.0154,0.9627,0.0094</t>
-  </si>
-  <si>
-    <t>0.9628,0.0462,0.0039,0.0020</t>
-  </si>
-  <si>
-    <t>0.9519,0.0519,0.0056,0.0032</t>
-  </si>
-  <si>
-    <t>0.9632,0.0289,0.0041,0.0041</t>
-  </si>
-  <si>
-    <t>0.0054,0.0432,0.9863,0.0044</t>
-  </si>
-  <si>
-    <t>0.9794,0.0104,0.0033,0.0033</t>
-  </si>
-  <si>
-    <t>0.9904,0.0062,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9604,0.0513,0.0043,0.0016</t>
-  </si>
-  <si>
-    <t>0.0362,0.4423,0.7726,0.0099</t>
-  </si>
-  <si>
-    <t>0.0729,0.0139,0.9193,0.0114</t>
-  </si>
-  <si>
-    <t>0.0160,0.0087,0.9688,0.0078</t>
-  </si>
-  <si>
-    <t>0.0047,0.6039,0.9307,0.0015</t>
-  </si>
-  <si>
-    <t>0.0053,0.0021,0.9920,0.0017</t>
-  </si>
-  <si>
-    <t>0.0240,0.9242,0.1139,0.0012</t>
-  </si>
-  <si>
-    <t>0.0037,0.9881,0.0193,0.0001</t>
-  </si>
-  <si>
-    <t>0.6144,0.1151,0.3751,0.0071</t>
-  </si>
-  <si>
-    <t>0.0254,0.4403,0.8664,0.0011</t>
-  </si>
-  <si>
-    <t>0.0128,0.0988,0.9662,0.0032</t>
-  </si>
-  <si>
-    <t>0.0104,0.3211,0.9443,0.0007</t>
-  </si>
-  <si>
-    <t>0.0091,0.4774,0.9118,0.0008</t>
-  </si>
-  <si>
-    <t>0.0117,0.9412,0.1527,0.0025</t>
-  </si>
-  <si>
-    <t>0.0219,0.5895,0.7032,0.0027</t>
-  </si>
-  <si>
-    <t>0.0164,0.0067,0.1050,0.9531</t>
-  </si>
-  <si>
-    <t>0.0064,0.0019,0.0006,0.9968</t>
-  </si>
-  <si>
-    <t>0.0053,0.0037,0.0016,0.9964</t>
-  </si>
-  <si>
-    <t>0.0124,0.0164,0.0179,0.9831</t>
-  </si>
-  <si>
-    <t>0.0496,0.0046,0.0119,0.9675</t>
-  </si>
-  <si>
-    <t>0.0096,0.0023,0.0064,0.9915</t>
-  </si>
-  <si>
-    <t>0.0113,0.6512,0.8261,0.0021</t>
-  </si>
-  <si>
-    <t>0.0337,0.1772,0.9144,0.0022</t>
-  </si>
-  <si>
-    <t>0.0634,0.1001,0.9044,0.0024</t>
-  </si>
-  <si>
-    <t>0.0984,0.0181,0.9173,0.0039</t>
-  </si>
-  <si>
-    <t>0.0072,0.6815,0.8159,0.0007</t>
-  </si>
-  <si>
-    <t>0.0465,0.3720,0.8306,0.0078</t>
-  </si>
-  <si>
-    <t>0.9917,0.0055,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9833,0.0151,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9526,0.0667,0.0050,0.0017</t>
-  </si>
-  <si>
-    <t>0.9885,0.0093,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9832,0.0135,0.0020,0.0014</t>
-  </si>
-  <si>
-    <t>0.9958,0.0018,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9591,0.0446,0.0051,0.0023</t>
-  </si>
-  <si>
-    <t>0.9460,0.0728,0.0056,0.0022</t>
-  </si>
-  <si>
-    <t>0.9896,0.0061,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9918,0.0048,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9944,0.0024,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9951,0.0015,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9927,0.0037,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9943,0.0023,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9963,0.0007,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9958,0.0011,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.0065,0.0009,0.9920,0.0016</t>
-  </si>
-  <si>
-    <t>0.0511,0.0086,0.9629,0.0016</t>
-  </si>
-  <si>
-    <t>0.4930,0.0293,0.0775,0.3616</t>
-  </si>
-  <si>
-    <t>0.1819,0.0110,0.8967,0.0023</t>
-  </si>
-  <si>
-    <t>0.0261,0.9654,0.0107,0.0011</t>
-  </si>
-  <si>
-    <t>0.0514,0.9354,0.0231,0.0020</t>
-  </si>
-  <si>
-    <t>0.2253,0.8271,0.0100,0.0038</t>
-  </si>
-  <si>
-    <t>0.0912,0.9003,0.0253,0.0015</t>
-  </si>
-  <si>
-    <t>0.0342,0.9525,0.0139,0.0022</t>
-  </si>
-  <si>
-    <t>0.0151,0.9675,0.0233,0.0016</t>
-  </si>
-  <si>
-    <t>0.7979,0.2552,0.0232,0.0060</t>
-  </si>
-  <si>
-    <t>0.6584,0.1476,0.2034,0.0150</t>
-  </si>
-  <si>
-    <t>0.5266,0.0251,0.6167,0.0049</t>
-  </si>
-  <si>
-    <t>0.7379,0.0211,0.2540,0.0144</t>
-  </si>
-  <si>
-    <t>0.7388,0.0294,0.3048,0.0095</t>
-  </si>
-  <si>
-    <t>0.6140,0.0620,0.1260,0.2754</t>
-  </si>
-  <si>
-    <t>0.0495,0.9490,0.0258,0.0005</t>
-  </si>
-  <si>
-    <t>0.0112,0.9580,0.1860,0.0007</t>
-  </si>
-  <si>
-    <t>0.0538,0.8906,0.1498,0.0084</t>
-  </si>
-  <si>
-    <t>0.0018,0.8693,0.8810,0.0006</t>
-  </si>
-  <si>
-    <t>0.0874,0.8713,0.1047,0.0009</t>
-  </si>
-  <si>
-    <t>0.4112,0.6252,0.0417,0.0015</t>
-  </si>
-  <si>
-    <t>0.2833,0.7481,0.0397,0.0014</t>
-  </si>
-  <si>
-    <t>0.9810,0.0140,0.0028,0.0020</t>
-  </si>
-  <si>
-    <t>0.9589,0.0292,0.0059,0.0060</t>
-  </si>
-  <si>
-    <t>0.9815,0.0133,0.0017,0.0021</t>
-  </si>
-  <si>
-    <t>0.9700,0.0073,0.0069,0.0081</t>
-  </si>
-  <si>
-    <t>0.9919,0.0020,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9759,0.0181,0.0094,0.0013</t>
-  </si>
-  <si>
-    <t>0.9664,0.0239,0.0031,0.0043</t>
-  </si>
-  <si>
-    <t>0.9507,0.0211,0.0050,0.0103</t>
-  </si>
-  <si>
-    <t>0.0197,0.0239,0.9743,0.0016</t>
-  </si>
-  <si>
-    <t>0.0040,0.4068,0.9612,0.0003</t>
-  </si>
-  <si>
-    <t>0.0745,0.1322,0.8331,0.0048</t>
-  </si>
-  <si>
-    <t>0.0699,0.0148,0.9570,0.0004</t>
-  </si>
-  <si>
-    <t>0.6107,0.0878,0.3049,0.0367</t>
-  </si>
-  <si>
-    <t>0.6955,0.0577,0.3127,0.0077</t>
-  </si>
-  <si>
-    <t>0.3374,0.0276,0.7956,0.0023</t>
-  </si>
-  <si>
-    <t>0.5484,0.2283,0.2838,0.0149</t>
-  </si>
-  <si>
-    <t>0.0593,0.0087,0.0070,0.9686</t>
-  </si>
-  <si>
-    <t>0.0010,0.0023,0.0055,0.9977</t>
-  </si>
-  <si>
-    <t>0.0054,0.0131,0.0051,0.9940</t>
-  </si>
-  <si>
-    <t>0.0155,0.0013,0.0024,0.9920</t>
-  </si>
-  <si>
-    <t>0.0036,0.1763,0.9765,0.0008</t>
-  </si>
-  <si>
-    <t>0.9537,0.0325,0.0110,0.0050</t>
-  </si>
-  <si>
-    <t>0.1722,0.8589,0.0094,0.0035</t>
-  </si>
-  <si>
-    <t>0.9739,0.0127,0.0016,0.0052</t>
-  </si>
-  <si>
-    <t>0.4452,0.6370,0.0281,0.0069</t>
-  </si>
-  <si>
-    <t>0.9545,0.0137,0.0189,0.0076</t>
-  </si>
-  <si>
-    <t>0.7221,0.0121,0.0235,0.2641</t>
-  </si>
-  <si>
-    <t>0.9692,0.0129,0.0023,0.0071</t>
-  </si>
-  <si>
-    <t>0.0019,0.3739,0.9590,0.0089</t>
-  </si>
-  <si>
-    <t>0.8495,0.0040,0.0033,0.1878</t>
-  </si>
-  <si>
-    <t>0.9523,0.0075,0.0064,0.0229</t>
-  </si>
-  <si>
-    <t>0.7689,0.1783,0.0682,0.0141</t>
-  </si>
-  <si>
-    <t>0.8288,0.0685,0.0865,0.0086</t>
-  </si>
-  <si>
-    <t>0.8356,0.1313,0.0417,0.0019</t>
-  </si>
-  <si>
-    <t>0.2216,0.5396,0.4001,0.0228</t>
-  </si>
-  <si>
-    <t>0.6083,0.1923,0.2542,0.0114</t>
-  </si>
-  <si>
-    <t>0.5133,0.4567,0.0874,0.0047</t>
-  </si>
-  <si>
-    <t>0.9875,0.0110,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9491,0.0450,0.0046,0.0069</t>
-  </si>
-  <si>
-    <t>0.9910,0.0026,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9836,0.0069,0.0013,0.0031</t>
-  </si>
-  <si>
-    <t>0.9898,0.0040,0.0010,0.0017</t>
-  </si>
-  <si>
-    <t>0.9828,0.0118,0.0016,0.0019</t>
-  </si>
-  <si>
-    <t>0.9811,0.0100,0.0017,0.0029</t>
-  </si>
-  <si>
-    <t>0.9820,0.0079,0.0015,0.0035</t>
-  </si>
-  <si>
-    <t>0.1336,0.7125,0.2910,0.0031</t>
-  </si>
-  <si>
-    <t>0.6354,0.5420,0.0098,0.0018</t>
-  </si>
-  <si>
-    <t>0.6863,0.4571,0.0104,0.0021</t>
-  </si>
-  <si>
-    <t>0.5143,0.2793,0.2632,0.0075</t>
-  </si>
-  <si>
-    <t>0.9440,0.0805,0.0067,0.0016</t>
-  </si>
-  <si>
-    <t>0.6912,0.4122,0.0186,0.0036</t>
-  </si>
-  <si>
-    <t>0.9420,0.0587,0.0085,0.0040</t>
-  </si>
-  <si>
-    <t>0.9517,0.0439,0.0068,0.0037</t>
-  </si>
-  <si>
-    <t>0.0012,0.1180,0.9939,0.0003</t>
-  </si>
-  <si>
-    <t>0.9516,0.0467,0.0073,0.0039</t>
-  </si>
-  <si>
-    <t>0.0106,0.0035,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0171,0.0123,0.9817,0.0006</t>
-  </si>
-  <si>
-    <t>0.2800,0.0114,0.8635,0.0009</t>
-  </si>
-  <si>
-    <t>0.0138,0.0380,0.9706,0.0029</t>
-  </si>
-  <si>
-    <t>0.1039,0.0245,0.9155,0.0017</t>
-  </si>
-  <si>
-    <t>0.0192,0.0050,0.9852,0.0007</t>
-  </si>
-  <si>
-    <t>0.1108,0.0117,0.9225,0.0024</t>
-  </si>
-  <si>
-    <t>0.1971,0.1460,0.7024,0.0042</t>
-  </si>
-  <si>
-    <t>0.3363,0.1273,0.5911,0.0069</t>
-  </si>
-  <si>
-    <t>0.7007,0.0709,0.2647,0.0117</t>
-  </si>
-  <si>
-    <t>0.4593,0.0700,0.5385,0.0037</t>
-  </si>
-  <si>
-    <t>0.1366,0.7027,0.1992,0.0048</t>
-  </si>
-  <si>
-    <t>0.2273,0.1100,0.6890,0.0083</t>
-  </si>
-  <si>
-    <t>0.6597,0.0964,0.2335,0.0448</t>
-  </si>
-  <si>
-    <t>0.3353,0.0791,0.6964,0.0068</t>
-  </si>
-  <si>
-    <t>0.9603,0.0522,0.0032,0.0017</t>
-  </si>
-  <si>
-    <t>0.5233,0.5932,0.0165,0.0014</t>
-  </si>
-  <si>
-    <t>0.8309,0.3019,0.0076,0.0010</t>
-  </si>
-  <si>
-    <t>0.9692,0.0473,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.6454,0.4782,0.0157,0.0026</t>
-  </si>
-  <si>
-    <t>0.4732,0.1722,0.3854,0.0094</t>
-  </si>
-  <si>
-    <t>0.5644,0.0232,0.5280,0.0139</t>
-  </si>
-  <si>
-    <t>0.7891,0.0286,0.1780,0.0148</t>
-  </si>
-  <si>
-    <t>0.5145,0.0232,0.5888,0.0122</t>
-  </si>
-  <si>
-    <t>0.4850,0.0147,0.6673,0.0082</t>
-  </si>
-  <si>
-    <t>0.1679,0.0420,0.7208,0.1786</t>
-  </si>
-  <si>
-    <t>0.1030,0.0462,0.8878,0.0049</t>
-  </si>
-  <si>
-    <t>0.0927,0.0119,0.9281,0.0025</t>
-  </si>
-  <si>
-    <t>0.1258,0.0184,0.8877,0.0066</t>
-  </si>
-  <si>
-    <t>0.0376,0.0334,0.9319,0.0097</t>
-  </si>
-  <si>
-    <t>0.9845,0.0077,0.0015,0.0026</t>
-  </si>
-  <si>
-    <t>0.9834,0.0125,0.0012,0.0020</t>
-  </si>
-  <si>
-    <t>0.9531,0.0535,0.0056,0.0023</t>
-  </si>
-  <si>
-    <t>0.9698,0.0393,0.0027,0.0014</t>
-  </si>
-  <si>
-    <t>0.9769,0.0228,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.9849,0.0145,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9819,0.0106,0.0012,0.0030</t>
-  </si>
-  <si>
-    <t>0.9753,0.0225,0.0033,0.0022</t>
-  </si>
-  <si>
-    <t>0.0839,0.0218,0.9378,0.0046</t>
-  </si>
-  <si>
-    <t>0.2951,0.3982,0.3334,0.0029</t>
-  </si>
-  <si>
-    <t>0.8622,0.0329,0.0893,0.0164</t>
-  </si>
-  <si>
-    <t>0.0303,0.0033,0.9753,0.0018</t>
-  </si>
-  <si>
-    <t>0.0152,0.0238,0.9781,0.0020</t>
-  </si>
-  <si>
-    <t>0.0975,0.0168,0.9320,0.0010</t>
-  </si>
-  <si>
-    <t>0.0066,0.0060,0.9926,0.0003</t>
-  </si>
-  <si>
-    <t>0.4004,0.0248,0.6981,0.0075</t>
-  </si>
-  <si>
-    <t>0.0054,0.0024,0.9917,0.0015</t>
-  </si>
-  <si>
-    <t>0.0279,0.0071,0.9712,0.0019</t>
-  </si>
-  <si>
-    <t>0.0277,0.0651,0.9541,0.0033</t>
-  </si>
-  <si>
-    <t>0.6839,0.0444,0.3238,0.0095</t>
-  </si>
-  <si>
-    <t>0.7136,0.0287,0.3169,0.0114</t>
-  </si>
-  <si>
-    <t>0.7818,0.0144,0.1702,0.0260</t>
-  </si>
-  <si>
-    <t>0.9670,0.0335,0.0023,0.0023</t>
-  </si>
-  <si>
-    <t>0.9866,0.0147,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9923,0.0070,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9747,0.0306,0.0020,0.0014</t>
-  </si>
-  <si>
-    <t>0.9924,0.0033,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9769,0.0233,0.0027,0.0014</t>
-  </si>
-  <si>
-    <t>0.9781,0.0244,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.9898,0.0061,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.0231,0.0390,0.9542,0.0027</t>
-  </si>
-  <si>
-    <t>0.0329,0.0724,0.9295,0.0070</t>
-  </si>
-  <si>
-    <t>0.0220,0.0197,0.9707,0.0016</t>
-  </si>
-  <si>
-    <t>0.0536,0.0539,0.9139,0.0039</t>
-  </si>
-  <si>
-    <t>0.0066,0.0021,0.9875,0.0036</t>
-  </si>
-  <si>
-    <t>0.4244,0.0162,0.6137,0.0353</t>
-  </si>
-  <si>
-    <t>0.4599,0.0227,0.6520,0.0115</t>
-  </si>
-  <si>
-    <t>0.0930,0.0197,0.8912,0.0159</t>
-  </si>
-  <si>
-    <t>0.8014,0.0010,0.0037,0.2289</t>
-  </si>
-  <si>
-    <t>0.0239,0.0302,0.0031,0.9848</t>
-  </si>
-  <si>
-    <t>0.0530,0.0104,0.0089,0.9679</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.0011,0.9980</t>
-  </si>
-  <si>
-    <t>0.0020,0.0009,0.0049,0.9969</t>
-  </si>
-  <si>
-    <t>0.5657,0.0348,0.0256,0.4454</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7472,0.1167,0.1199,0.0416</t>
+  </si>
+  <si>
+    <t>0.0115,0.0032,0.0010,0.9946</t>
+  </si>
+  <si>
+    <t>0.8657,0.0371,0.0151,0.0741</t>
+  </si>
+  <si>
+    <t>0.1070,0.0185,0.0100,0.9427</t>
+  </si>
+  <si>
+    <t>0.9895,0.0097,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9862,0.0084,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9786,0.0191,0.0025,0.0017</t>
+  </si>
+  <si>
+    <t>0.9862,0.0081,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.9916,0.0040,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9797,0.0130,0.0021,0.0031</t>
+  </si>
+  <si>
+    <t>0.9936,0.0047,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0022,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.6359,0.0452,0.3893,0.0145</t>
+  </si>
+  <si>
+    <t>0.2415,0.0579,0.7964,0.0048</t>
+  </si>
+  <si>
+    <t>0.4067,0.0677,0.6032,0.0020</t>
+  </si>
+  <si>
+    <t>0.3077,0.0256,0.7817,0.0027</t>
+  </si>
+  <si>
+    <t>0.4570,0.1574,0.4054,0.0080</t>
+  </si>
+  <si>
+    <t>0.0221,0.9710,0.0219,0.0002</t>
+  </si>
+  <si>
+    <t>0.0118,0.9795,0.0202,0.0003</t>
+  </si>
+  <si>
+    <t>0.3161,0.7774,0.0185,0.0014</t>
+  </si>
+  <si>
+    <t>0.0273,0.9665,0.0146,0.0005</t>
+  </si>
+  <si>
+    <t>0.0101,0.9808,0.0244,0.0003</t>
+  </si>
+  <si>
+    <t>0.4133,0.0238,0.6898,0.0056</t>
+  </si>
+  <si>
+    <t>0.5580,0.0215,0.5825,0.0044</t>
+  </si>
+  <si>
+    <t>0.0580,0.0102,0.9412,0.0067</t>
+  </si>
+  <si>
+    <t>0.3660,0.0251,0.7419,0.0046</t>
+  </si>
+  <si>
+    <t>0.1721,0.0103,0.9081,0.0019</t>
+  </si>
+  <si>
+    <t>0.2711,0.0092,0.7863,0.0162</t>
+  </si>
+  <si>
+    <t>0.0091,0.0020,0.9814,0.0099</t>
+  </si>
+  <si>
+    <t>0.6109,0.2490,0.1596,0.0101</t>
+  </si>
+  <si>
+    <t>0.3238,0.3467,0.4206,0.0142</t>
+  </si>
+  <si>
+    <t>0.0018,0.0147,0.9917,0.0063</t>
+  </si>
+  <si>
+    <t>0.0084,0.8950,0.3790,0.0003</t>
+  </si>
+  <si>
+    <t>0.8416,0.0922,0.0471,0.0265</t>
+  </si>
+  <si>
+    <t>0.8699,0.1177,0.0280,0.0095</t>
+  </si>
+  <si>
+    <t>0.6069,0.4779,0.0274,0.0014</t>
+  </si>
+  <si>
+    <t>0.0974,0.8215,0.1928,0.0034</t>
+  </si>
+  <si>
+    <t>0.1292,0.4389,0.4248,0.1259</t>
+  </si>
+  <si>
+    <t>0.0314,0.0097,0.9154,0.0547</t>
+  </si>
+  <si>
+    <t>0.0454,0.0111,0.9533,0.0036</t>
+  </si>
+  <si>
+    <t>0.0938,0.0080,0.9263,0.0044</t>
+  </si>
+  <si>
+    <t>0.0206,0.0871,0.9568,0.0011</t>
+  </si>
+  <si>
+    <t>0.0401,0.7470,0.3788,0.0055</t>
+  </si>
+  <si>
+    <t>0.0819,0.0581,0.8720,0.0236</t>
+  </si>
+  <si>
+    <t>0.1175,0.0874,0.0165,0.9255</t>
+  </si>
+  <si>
+    <t>0.1176,0.8803,0.0464,0.0015</t>
+  </si>
+  <si>
+    <t>0.0095,0.9573,0.2004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0187,0.9276,0.2787,0.0018</t>
+  </si>
+  <si>
+    <t>0.0060,0.0356,0.9816,0.0053</t>
+  </si>
+  <si>
+    <t>0.0139,0.0488,0.9741,0.0022</t>
+  </si>
+  <si>
+    <t>0.3061,0.0030,0.8512,0.0014</t>
+  </si>
+  <si>
+    <t>0.1138,0.0043,0.9164,0.0078</t>
+  </si>
+  <si>
+    <t>0.0146,0.0165,0.9804,0.0015</t>
+  </si>
+  <si>
+    <t>0.0248,0.0152,0.9647,0.0055</t>
+  </si>
+  <si>
+    <t>0.9724,0.0228,0.0031,0.0025</t>
+  </si>
+  <si>
+    <t>0.9561,0.0345,0.0076,0.0047</t>
+  </si>
+  <si>
+    <t>0.9034,0.1276,0.0117,0.0029</t>
+  </si>
+  <si>
+    <t>0.0018,0.0145,0.9943,0.0035</t>
+  </si>
+  <si>
+    <t>0.9772,0.0171,0.0025,0.0028</t>
+  </si>
+  <si>
+    <t>0.9810,0.0148,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.8599,0.2230,0.0064,0.0029</t>
+  </si>
+  <si>
+    <t>0.0329,0.4347,0.8206,0.0090</t>
+  </si>
+  <si>
+    <t>0.0107,0.0141,0.9727,0.0099</t>
+  </si>
+  <si>
+    <t>0.0091,0.0289,0.9688,0.0118</t>
+  </si>
+  <si>
+    <t>0.0027,0.7703,0.9096,0.0004</t>
+  </si>
+  <si>
+    <t>0.0174,0.0065,0.9818,0.0015</t>
+  </si>
+  <si>
+    <t>0.0333,0.8621,0.2303,0.0024</t>
+  </si>
+  <si>
+    <t>0.0065,0.9856,0.0082,0.0001</t>
+  </si>
+  <si>
+    <t>0.3156,0.0758,0.7434,0.0070</t>
+  </si>
+  <si>
+    <t>0.7878,0.1289,0.1034,0.0064</t>
+  </si>
+  <si>
+    <t>0.0074,0.0216,0.9867,0.0031</t>
+  </si>
+  <si>
+    <t>0.0288,0.1987,0.9084,0.0040</t>
+  </si>
+  <si>
+    <t>0.0059,0.2478,0.9648,0.0003</t>
+  </si>
+  <si>
+    <t>0.0245,0.5025,0.7491,0.0018</t>
+  </si>
+  <si>
+    <t>0.0074,0.6726,0.8393,0.0013</t>
+  </si>
+  <si>
+    <t>0.0066,0.0017,0.0108,0.9914</t>
+  </si>
+  <si>
+    <t>0.0152,0.0029,0.0004,0.9945</t>
+  </si>
+  <si>
+    <t>0.0012,0.0717,0.0015,0.9970</t>
+  </si>
+  <si>
+    <t>0.0324,0.0150,0.0070,0.9791</t>
+  </si>
+  <si>
+    <t>0.0147,0.0032,0.0385,0.9743</t>
+  </si>
+  <si>
+    <t>0.0229,0.0090,0.0017,0.9891</t>
+  </si>
+  <si>
+    <t>0.0065,0.7353,0.8445,0.0011</t>
+  </si>
+  <si>
+    <t>0.0168,0.0644,0.9633,0.0035</t>
+  </si>
+  <si>
+    <t>0.0555,0.0843,0.9018,0.0071</t>
+  </si>
+  <si>
+    <t>0.0092,0.5205,0.8811,0.0012</t>
+  </si>
+  <si>
+    <t>0.0050,0.8835,0.6360,0.0006</t>
+  </si>
+  <si>
+    <t>0.0575,0.0543,0.9406,0.0010</t>
+  </si>
+  <si>
+    <t>0.9837,0.0161,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9578,0.0640,0.0039,0.0013</t>
+  </si>
+  <si>
+    <t>0.9628,0.0420,0.0043,0.0016</t>
+  </si>
+  <si>
+    <t>0.9835,0.0134,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9855,0.0084,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.9929,0.0030,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9799,0.0207,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9853,0.0103,0.0014,0.0017</t>
+  </si>
+  <si>
+    <t>0.9957,0.0021,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9922,0.0026,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9925,0.0029,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9924,0.0035,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9890,0.0049,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9928,0.0041,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9955,0.0023,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0112,0.0029,0.9750,0.0195</t>
+  </si>
+  <si>
+    <t>0.0390,0.0077,0.9771,0.0005</t>
+  </si>
+  <si>
+    <t>0.7818,0.0304,0.1744,0.0196</t>
+  </si>
+  <si>
+    <t>0.3954,0.0264,0.6967,0.0023</t>
+  </si>
+  <si>
+    <t>0.0146,0.9710,0.0243,0.0011</t>
+  </si>
+  <si>
+    <t>0.0545,0.9275,0.0342,0.0012</t>
+  </si>
+  <si>
+    <t>0.4778,0.6338,0.0169,0.0022</t>
+  </si>
+  <si>
+    <t>0.3695,0.7095,0.0276,0.0033</t>
+  </si>
+  <si>
+    <t>0.0439,0.9459,0.0224,0.0019</t>
+  </si>
+  <si>
+    <t>0.0141,0.9789,0.0067,0.0007</t>
+  </si>
+  <si>
+    <t>0.7987,0.2905,0.0163,0.0028</t>
+  </si>
+  <si>
+    <t>0.6469,0.2001,0.1151,0.0412</t>
+  </si>
+  <si>
+    <t>0.4364,0.0321,0.6401,0.0138</t>
+  </si>
+  <si>
+    <t>0.6737,0.1272,0.2209,0.0061</t>
+  </si>
+  <si>
+    <t>0.4242,0.0672,0.5851,0.0134</t>
+  </si>
+  <si>
+    <t>0.4427,0.3008,0.1101,0.3257</t>
+  </si>
+  <si>
+    <t>0.0128,0.9683,0.0927,0.0003</t>
+  </si>
+  <si>
+    <t>0.0124,0.9679,0.0549,0.0008</t>
+  </si>
+  <si>
+    <t>0.0838,0.8200,0.1225,0.0149</t>
+  </si>
+  <si>
+    <t>0.0046,0.8823,0.7634,0.0029</t>
+  </si>
+  <si>
+    <t>0.0673,0.8897,0.1294,0.0015</t>
+  </si>
+  <si>
+    <t>0.5050,0.5694,0.0360,0.0027</t>
+  </si>
+  <si>
+    <t>0.1151,0.8530,0.0719,0.0022</t>
+  </si>
+  <si>
+    <t>0.9734,0.0126,0.0055,0.0039</t>
+  </si>
+  <si>
+    <t>0.9743,0.0041,0.0013,0.0130</t>
+  </si>
+  <si>
+    <t>0.9841,0.0060,0.0014,0.0038</t>
+  </si>
+  <si>
+    <t>0.9597,0.0265,0.0047,0.0074</t>
+  </si>
+  <si>
+    <t>0.9901,0.0048,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9804,0.0097,0.0049,0.0024</t>
+  </si>
+  <si>
+    <t>0.9877,0.0039,0.0013,0.0028</t>
+  </si>
+  <si>
+    <t>0.9845,0.0066,0.0020,0.0026</t>
+  </si>
+  <si>
+    <t>0.0161,0.1926,0.9364,0.0018</t>
+  </si>
+  <si>
+    <t>0.0106,0.4314,0.9068,0.0007</t>
+  </si>
+  <si>
+    <t>0.0414,0.1039,0.9117,0.0019</t>
+  </si>
+  <si>
+    <t>0.0669,0.0693,0.9000,0.0010</t>
+  </si>
+  <si>
+    <t>0.4799,0.0829,0.4922,0.0771</t>
+  </si>
+  <si>
+    <t>0.5476,0.1015,0.3854,0.0086</t>
+  </si>
+  <si>
+    <t>0.3147,0.0119,0.7799,0.0108</t>
+  </si>
+  <si>
+    <t>0.7179,0.0920,0.2217,0.0105</t>
+  </si>
+  <si>
+    <t>0.1711,0.0125,0.0098,0.9097</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.0012,0.9993</t>
+  </si>
+  <si>
+    <t>0.0017,0.0156,0.0007,0.9981</t>
+  </si>
+  <si>
+    <t>0.0204,0.0110,0.0055,0.9864</t>
+  </si>
+  <si>
+    <t>0.0125,0.2502,0.9236,0.0055</t>
+  </si>
+  <si>
+    <t>0.9837,0.0054,0.0019,0.0034</t>
+  </si>
+  <si>
+    <t>0.2815,0.7549,0.0360,0.0078</t>
+  </si>
+  <si>
+    <t>0.9770,0.0130,0.0020,0.0027</t>
+  </si>
+  <si>
+    <t>0.7021,0.4652,0.0096,0.0020</t>
+  </si>
+  <si>
+    <t>0.9570,0.0185,0.0101,0.0064</t>
+  </si>
+  <si>
+    <t>0.6950,0.0289,0.0249,0.3064</t>
+  </si>
+  <si>
+    <t>0.9808,0.0064,0.0015,0.0046</t>
+  </si>
+  <si>
+    <t>0.0021,0.0926,0.9745,0.0171</t>
+  </si>
+  <si>
+    <t>0.8737,0.0017,0.0047,0.1238</t>
+  </si>
+  <si>
+    <t>0.9146,0.0362,0.0157,0.0222</t>
+  </si>
+  <si>
+    <t>0.7392,0.2836,0.0319,0.0134</t>
+  </si>
+  <si>
+    <t>0.8262,0.0731,0.1015,0.0085</t>
+  </si>
+  <si>
+    <t>0.8545,0.0404,0.1083,0.0088</t>
+  </si>
+  <si>
+    <t>0.4076,0.5460,0.0915,0.0136</t>
+  </si>
+  <si>
+    <t>0.5353,0.4433,0.0821,0.0040</t>
+  </si>
+  <si>
+    <t>0.6666,0.2259,0.1270,0.0056</t>
+  </si>
+  <si>
+    <t>0.9936,0.0033,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9864,0.0057,0.0015,0.0031</t>
+  </si>
+  <si>
+    <t>0.9852,0.0075,0.0007,0.0023</t>
+  </si>
+  <si>
+    <t>0.9860,0.0054,0.0014,0.0030</t>
+  </si>
+  <si>
+    <t>0.9604,0.0253,0.0067,0.0068</t>
+  </si>
+  <si>
+    <t>0.9402,0.0578,0.0063,0.0055</t>
+  </si>
+  <si>
+    <t>0.9831,0.0075,0.0012,0.0026</t>
+  </si>
+  <si>
+    <t>0.9739,0.0153,0.0026,0.0043</t>
+  </si>
+  <si>
+    <t>0.6730,0.4174,0.0257,0.0026</t>
+  </si>
+  <si>
+    <t>0.7409,0.3801,0.0109,0.0029</t>
+  </si>
+  <si>
+    <t>0.7752,0.3335,0.0119,0.0029</t>
+  </si>
+  <si>
+    <t>0.6464,0.3066,0.1050,0.0102</t>
+  </si>
+  <si>
+    <t>0.9233,0.0938,0.0076,0.0039</t>
+  </si>
+  <si>
+    <t>0.9066,0.0682,0.0156,0.0112</t>
+  </si>
+  <si>
+    <t>0.9627,0.0417,0.0048,0.0021</t>
+  </si>
+  <si>
+    <t>0.9462,0.0559,0.0095,0.0036</t>
+  </si>
+  <si>
+    <t>0.0031,0.1430,0.9842,0.0011</t>
+  </si>
+  <si>
+    <t>0.9177,0.0928,0.0148,0.0039</t>
+  </si>
+  <si>
+    <t>0.0028,0.0027,0.9950,0.0006</t>
+  </si>
+  <si>
+    <t>0.0065,0.0543,0.9838,0.0015</t>
+  </si>
+  <si>
+    <t>0.0795,0.0171,0.9346,0.0050</t>
+  </si>
+  <si>
+    <t>0.0410,0.0417,0.9367,0.0050</t>
+  </si>
+  <si>
+    <t>0.0532,0.0576,0.9262,0.0024</t>
+  </si>
+  <si>
+    <t>0.0128,0.0129,0.9877,0.0003</t>
+  </si>
+  <si>
+    <t>0.0598,0.0065,0.9548,0.0036</t>
+  </si>
+  <si>
+    <t>0.3322,0.1146,0.5949,0.0085</t>
+  </si>
+  <si>
+    <t>0.0632,0.1221,0.8900,0.0022</t>
+  </si>
+  <si>
+    <t>0.4212,0.0623,0.6158,0.0094</t>
+  </si>
+  <si>
+    <t>0.1936,0.3704,0.4422,0.0027</t>
+  </si>
+  <si>
+    <t>0.1160,0.6470,0.2945,0.0105</t>
+  </si>
+  <si>
+    <t>0.3053,0.2681,0.4630,0.0064</t>
+  </si>
+  <si>
+    <t>0.5701,0.3922,0.0715,0.0182</t>
+  </si>
+  <si>
+    <t>0.2229,0.2541,0.5970,0.0103</t>
+  </si>
+  <si>
+    <t>0.7465,0.3920,0.0108,0.0010</t>
+  </si>
+  <si>
+    <t>0.9151,0.1502,0.0048,0.0017</t>
+  </si>
+  <si>
+    <t>0.2232,0.8229,0.0171,0.0015</t>
+  </si>
+  <si>
+    <t>0.9637,0.0478,0.0025,0.0015</t>
+  </si>
+  <si>
+    <t>0.2387,0.8393,0.0125,0.0009</t>
+  </si>
+  <si>
+    <t>0.6903,0.1368,0.1826,0.0091</t>
+  </si>
+  <si>
+    <t>0.6642,0.0577,0.3615,0.0061</t>
+  </si>
+  <si>
+    <t>0.6498,0.0588,0.3029,0.0463</t>
+  </si>
+  <si>
+    <t>0.3654,0.0129,0.7324,0.0148</t>
+  </si>
+  <si>
+    <t>0.6305,0.0404,0.3798,0.0191</t>
+  </si>
+  <si>
+    <t>0.3088,0.0259,0.7563,0.0192</t>
+  </si>
+  <si>
+    <t>0.1349,0.0575,0.8372,0.0101</t>
+  </si>
+  <si>
+    <t>0.0690,0.0643,0.9060,0.0030</t>
+  </si>
+  <si>
+    <t>0.2860,0.0137,0.8118,0.0042</t>
+  </si>
+  <si>
+    <t>0.1370,0.0697,0.8331,0.0048</t>
+  </si>
+  <si>
+    <t>0.9871,0.0076,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.9483,0.0865,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.9787,0.0123,0.0026,0.0029</t>
+  </si>
+  <si>
+    <t>0.9827,0.0131,0.0020,0.0017</t>
+  </si>
+  <si>
+    <t>0.9696,0.0222,0.0029,0.0040</t>
+  </si>
+  <si>
+    <t>0.9727,0.0331,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9922,0.0028,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9774,0.0177,0.0029,0.0021</t>
+  </si>
+  <si>
+    <t>0.1473,0.0184,0.9022,0.0035</t>
+  </si>
+  <si>
+    <t>0.3939,0.2648,0.4318,0.0081</t>
+  </si>
+  <si>
+    <t>0.8512,0.0814,0.0852,0.0149</t>
+  </si>
+  <si>
+    <t>0.1602,0.0460,0.8489,0.0065</t>
+  </si>
+  <si>
+    <t>0.0094,0.0102,0.9807,0.0034</t>
+  </si>
+  <si>
+    <t>0.0541,0.0637,0.9268,0.0016</t>
+  </si>
+  <si>
+    <t>0.0074,0.0068,0.9891,0.0011</t>
+  </si>
+  <si>
+    <t>0.1070,0.0324,0.9019,0.0032</t>
+  </si>
+  <si>
+    <t>0.0120,0.0057,0.9790,0.0069</t>
+  </si>
+  <si>
+    <t>0.0436,0.0147,0.9607,0.0017</t>
+  </si>
+  <si>
+    <t>0.0343,0.1558,0.9256,0.0033</t>
+  </si>
+  <si>
+    <t>0.7069,0.0269,0.3745,0.0055</t>
+  </si>
+  <si>
+    <t>0.6120,0.0202,0.4854,0.0105</t>
+  </si>
+  <si>
+    <t>0.7961,0.0164,0.1791,0.0174</t>
+  </si>
+  <si>
+    <t>0.9622,0.0398,0.0044,0.0024</t>
+  </si>
+  <si>
+    <t>0.9833,0.0156,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9819,0.0219,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9633,0.0529,0.0029,0.0017</t>
+  </si>
+  <si>
+    <t>0.9859,0.0105,0.0013,0.0018</t>
+  </si>
+  <si>
+    <t>0.9735,0.0272,0.0027,0.0013</t>
+  </si>
+  <si>
+    <t>0.9720,0.0309,0.0037,0.0012</t>
+  </si>
+  <si>
+    <t>0.9862,0.0102,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.0967,0.0967,0.8409,0.0071</t>
+  </si>
+  <si>
+    <t>0.0093,0.0162,0.9808,0.0028</t>
+  </si>
+  <si>
+    <t>0.0529,0.0182,0.9505,0.0022</t>
+  </si>
+  <si>
+    <t>0.1499,0.0175,0.8948,0.0024</t>
+  </si>
+  <si>
+    <t>0.0046,0.0027,0.9891,0.0038</t>
+  </si>
+  <si>
+    <t>0.2536,0.0787,0.6613,0.1045</t>
+  </si>
+  <si>
+    <t>0.2787,0.0563,0.7110,0.0316</t>
+  </si>
+  <si>
+    <t>0.0902,0.0226,0.8477,0.0461</t>
+  </si>
+  <si>
+    <t>0.8746,0.0068,0.0516,0.0335</t>
+  </si>
+  <si>
+    <t>0.0232,0.0392,0.0022,0.9841</t>
+  </si>
+  <si>
+    <t>0.0760,0.0055,0.0018,0.9702</t>
+  </si>
+  <si>
+    <t>0.0119,0.0009,0.0036,0.9919</t>
+  </si>
+  <si>
+    <t>0.0019,0.0067,0.0004,0.9984</t>
+  </si>
+  <si>
+    <t>0.7299,0.0974,0.0475,0.1286</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2466,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4790,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
